--- a/tame_output/ON/bt/strategyON_20241001.xlsx
+++ b/tame_output/ON/bt/strategyON_20241001.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>48.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.1%</t>
+          <t>420.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-609.9%</t>
+          <t>-609.5%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-62.7%</t>
+          <t>-62.5%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-205.3%</t>
+          <t>-205.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-96.1%</t>
+          <t>-95.8%</t>
         </is>
       </c>
     </row>
@@ -1395,17 +1395,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>116.1%</t>
+          <t>115.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.8%</t>
         </is>
       </c>
     </row>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121464</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906077</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013422</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960217997</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
@@ -48994,7 +48994,7 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113276</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
@@ -49040,7 +49040,7 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236294</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
@@ -49224,7 +49224,7 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70520107942768</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889187</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
@@ -49362,7 +49362,7 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762282</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988013</v>
+        <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047742</v>
+        <v>3.821827147047743</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.309239980939155</v>
+        <v>-5.358803451984196</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.826175239740425</v>
+        <v>2.806349851322409</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.8104516018385071</v>
+        <v>0.7608881307934654</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.43649861753294</v>
+        <v>5.406760534905914</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650751</v>
+        <v>3.825268416650752</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.323995305139295</v>
+        <v>-5.373558776184336</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.815910694099566</v>
+        <v>2.796085305681549</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.8104516018385071</v>
+        <v>0.7608881307934654</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.432136201572137</v>
+        <v>5.402398118945111</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135745</v>
+        <v>3.845044666135746</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.274530681769384</v>
+        <v>-5.324094152814425</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.82662104686381</v>
+        <v>2.806795658445794</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8599162252084187</v>
+        <v>0.810352754163377</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.452739479010363</v>
+        <v>5.423001396383338</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479219</v>
+        <v>3.82593179047922</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.111422689615768</v>
+        <v>-5.160986160660809</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.888271911440191</v>
+        <v>2.868446523022175</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.023024217362034</v>
+        <v>0.9734607463169923</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.547011942017467</v>
+        <v>5.517273859390442</v>
       </c>
     </row>
     <row r="2097">
@@ -49782,16 +49782,16 @@
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.978615064118602</v>
+        <v>-5.028178535163643</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.950441998330186</v>
+        <v>2.930616609912169</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.023024217362034</v>
+        <v>0.9734607463169923</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.556058978708595</v>
+        <v>5.52632089608157</v>
       </c>
     </row>
     <row r="2098">
@@ -49805,16 +49805,16 @@
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.04132298059316</v>
+        <v>-5.090886451638201</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.926216296726484</v>
+        <v>2.906390908308468</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9603163008874763</v>
+        <v>0.9107528298424346</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.519291693809982</v>
+        <v>5.489553611182957</v>
       </c>
     </row>
     <row r="2099">
@@ -49828,16 +49828,16 @@
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.993314856749467</v>
+        <v>-5.042878327794508</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.908328963054314</v>
+        <v>2.888503574636297</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9603163008874763</v>
+        <v>0.9107528298424346</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.482201110600334</v>
+        <v>5.452463027973309</v>
       </c>
     </row>
     <row r="2100">
@@ -49851,16 +49851,16 @@
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.914489199565876</v>
+        <v>-4.964052670610918</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.9437914794857</v>
+        <v>2.923966091067683</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.039141958071067</v>
+        <v>0.9895784870260251</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.533428758468439</v>
+        <v>5.503690675841414</v>
       </c>
     </row>
     <row r="2101">
@@ -49874,16 +49874,16 @@
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.722554398312003</v>
+        <v>-4.772117869357044</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.015464492594286</v>
+        <v>2.99563910417627</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.039141958071067</v>
+        <v>0.9895784870260251</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.528327851075476</v>
+        <v>5.498589768448451</v>
       </c>
     </row>
     <row r="2102">
@@ -49897,16 +49897,16 @@
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.604381020294076</v>
+        <v>-4.653944491339116</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.058087753190552</v>
+        <v>3.038262364772536</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.157315336088994</v>
+        <v>1.107751865043952</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.594585787275327</v>
+        <v>5.564847704648303</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.718554117374829</v>
+        <v>3.763505853666238</v>
       </c>
       <c r="C2103" t="n">
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.483201935328069</v>
+        <v>-4.479378094730993</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.135647980039982</v>
+        <v>3.137177516278812</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.278494421055</v>
+        <v>1.282318261652076</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.696381831117958</v>
+        <v>5.698676135476203</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241001.xlsx
+++ b/tame_output/ON/bt/strategyON_20241001.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-72.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.7%</t>
+          <t>420.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-609.5%</t>
+          <t>-615.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-62.5%</t>
+          <t>-65.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-95.8%</t>
+          <t>-101.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>126.5%</t>
+          <t>125.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>115.8%</t>
+          <t>114.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>123.8%</t>
+          <t>120.2%</t>
         </is>
       </c>
     </row>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800096</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620433</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700998</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217997</v>
+        <v>3.715372960217999</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
@@ -48994,7 +48994,7 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353534</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113276</v>
+        <v>3.736822870113278</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72378970539411</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456727</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883676</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
@@ -49224,7 +49224,7 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
@@ -49270,7 +49270,7 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667452</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
@@ -49316,7 +49316,7 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409563</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
@@ -49339,7 +49339,7 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
@@ -49362,7 +49362,7 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988014</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
@@ -49408,7 +49408,7 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
@@ -49684,7 +49684,7 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047743</v>
+        <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
@@ -49707,7 +49707,7 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650752</v>
+        <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
@@ -49730,7 +49730,7 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135746</v>
+        <v>3.845044666135745</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
@@ -49753,7 +49753,7 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.82593179047922</v>
+        <v>3.825931790479219</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
@@ -49920,16 +49920,16 @@
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.479378094730993</v>
+        <v>-4.540529808556385</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.137177516278812</v>
+        <v>3.112716830748655</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.282318261652076</v>
+        <v>1.221166547826684</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.698676135476203</v>
+        <v>5.661985107180968</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241001.xlsx
+++ b/tame_output/ON/bt/strategyON_20241001.xlsx
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912982</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800096</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660848</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.689942600700998</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
@@ -48971,7 +48971,7 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217999</v>
+        <v>3.715372960217997</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
@@ -48994,7 +48994,7 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353534</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113278</v>
+        <v>3.736822870113276</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.794486844016436</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
@@ -49086,7 +49086,7 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307668</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715607446456726</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883676</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
@@ -49224,7 +49224,7 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427682</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610378</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
@@ -49270,7 +49270,7 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667451</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
@@ -49316,7 +49316,7 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409562</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
@@ -49339,7 +49339,7 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452568</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
@@ -49362,7 +49362,7 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762283</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988014</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
@@ -49408,7 +49408,7 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.647907242740918</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
@@ -49431,7 +49431,7 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
@@ -49454,7 +49454,7 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
@@ -49477,7 +49477,7 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
@@ -49500,7 +49500,7 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383088</v>
+        <v>3.735300721383086</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
@@ -49523,7 +49523,7 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720992</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
@@ -49546,7 +49546,7 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455268</v>
+        <v>3.775357097455267</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
@@ -49569,7 +49569,7 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963129</v>
+        <v>3.749078058963128</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
@@ -49592,7 +49592,7 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162539</v>
+        <v>3.740284389162538</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
@@ -49615,7 +49615,7 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652378</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
@@ -49638,7 +49638,7 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.80905590510867</v>
+        <v>3.809055905108668</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
@@ -49661,7 +49661,7 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.835202441103559</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
@@ -49684,7 +49684,7 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047742</v>
+        <v>3.821827147047741</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
@@ -49776,7 +49776,7 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844243</v>
+        <v>3.847096478844241</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
@@ -49799,7 +49799,7 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790947</v>
+        <v>3.832425987790945</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
@@ -49822,7 +49822,7 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578993</v>
+        <v>3.861579399578991</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
@@ -49845,7 +49845,7 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629881</v>
+        <v>3.872253907629879</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
@@ -49868,7 +49868,7 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686404</v>
+        <v>3.868502531686402</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
@@ -49891,7 +49891,7 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.84932404404671</v>
+        <v>3.849324044046709</v>
       </c>
       <c r="C2102" t="n">
         <v>4.900196585621931</v>
@@ -49914,7 +49914,7 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.763505853666238</v>
+        <v>3.763505853666237</v>
       </c>
       <c r="C2103" t="n">
         <v>4.929285178484958</v>

--- a/tame_output/ON/bt/strategyON_20241001.xlsx
+++ b/tame_output/ON/bt/strategyON_20241001.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>114.1%</t>
+          <t>113.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,16 +768,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>181.3%</t>
+          <t>179.7%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -982,12 +982,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>125.2%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>120.2%</t>
+          <t>44.6%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2103"/>
+  <dimension ref="A1:G2104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49914,7 +49914,7 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.763505853666237</v>
+        <v>3.836463274528998</v>
       </c>
       <c r="C2103" t="n">
         <v>4.929285178484958</v>
@@ -49930,6 +49930,29 @@
       </c>
       <c r="G2103" t="n">
         <v>5.661985107180968</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="2" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>3.762555340764562</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>4.91363342535514</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>-4.540529808556385</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>3.112716830748655</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>1.221166547826684</v>
+      </c>
+      <c r="G2104" t="n">
+        <v>4.906697222341508</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241001.xlsx
+++ b/tame_output/ON/bt/strategyON_20241001.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>59.4%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>113.4%</t>
+          <t>118.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>99.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>179.7%</t>
+          <t>194.8%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-30.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.0%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-72.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.6%</t>
+          <t>421.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-615.6%</t>
+          <t>-610.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-65.0%</t>
+          <t>-63.0%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-205.5%</t>
+          <t>-204.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>59.7%</t>
         </is>
       </c>
     </row>
@@ -49000,10 +49000,10 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.579159028320117</v>
+        <v>-5.530479913539902</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.681237446504676</v>
+        <v>1.700709092416762</v>
       </c>
       <c r="F2063" t="n">
         <v>0.6448782832176025</v>
@@ -49023,10 +49023,10 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.597377495317725</v>
+        <v>-5.548698380537511</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.673488423048565</v>
+        <v>1.692960068960651</v>
       </c>
       <c r="F2064" t="n">
         <v>0.6197718459617604</v>
@@ -49046,10 +49046,10 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.509170661170147</v>
+        <v>-5.460491546389933</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.728645549557915</v>
+        <v>1.748117195470001</v>
       </c>
       <c r="F2065" t="n">
         <v>0.6197718459617604</v>
@@ -49069,10 +49069,10 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.403135665964838</v>
+        <v>-5.354456551184623</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.754760248164767</v>
+        <v>1.774231894076852</v>
       </c>
       <c r="F2066" t="n">
         <v>0.6197718459617604</v>
@@ -49092,10 +49092,10 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.219924002831743</v>
+        <v>-5.171244888051528</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.830475862882051</v>
+        <v>1.849947508794136</v>
       </c>
       <c r="F2067" t="n">
         <v>0.6197718459617604</v>
@@ -49115,10 +49115,10 @@
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.148202555817892</v>
+        <v>-5.099523441037677</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.842108847766968</v>
+        <v>1.861580493679054</v>
       </c>
       <c r="F2068" t="n">
         <v>0.691493292975611</v>
@@ -49138,10 +49138,10 @@
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.125829530210186</v>
+        <v>-5.077150415429971</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.797973803931222</v>
+        <v>1.817445449843308</v>
       </c>
       <c r="F2069" t="n">
         <v>0.7027490440885126</v>
@@ -49161,10 +49161,10 @@
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.15884582612093</v>
+        <v>-5.110166711340716</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.969965490452279</v>
+        <v>1.989437136364365</v>
       </c>
       <c r="F2070" t="n">
         <v>0.6333116674217609</v>
@@ -49184,10 +49184,10 @@
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.147318190471322</v>
+        <v>-5.098639075691107</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.966497770540372</v>
+        <v>1.985969416452458</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6923123256231234</v>
@@ -49207,10 +49207,10 @@
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.24465969181369</v>
+        <v>-5.195980577033476</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.931229282525213</v>
+        <v>1.950700928437299</v>
       </c>
       <c r="F2072" t="n">
         <v>0.647892143457635</v>
@@ -49230,10 +49230,10 @@
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.330515721153657</v>
+        <v>-5.281836606373442</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.898137952982065</v>
+        <v>1.91760959889415</v>
       </c>
       <c r="F2073" t="n">
         <v>0.6055160742315</v>
@@ -49253,10 +49253,10 @@
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.339352518569776</v>
+        <v>-5.290673403789562</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.877022435836119</v>
+        <v>1.896494081748205</v>
       </c>
       <c r="F2074" t="n">
         <v>0.5980739015901493</v>
@@ -49276,10 +49276,10 @@
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.430735081135235</v>
+        <v>-5.38205596635502</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.850633921854985</v>
+        <v>1.870105567767071</v>
       </c>
       <c r="F2075" t="n">
         <v>0.5615090168708046</v>
@@ -49299,10 +49299,10 @@
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.419028363148229</v>
+        <v>-5.370349248368014</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.957444866874055</v>
+        <v>1.976916512786141</v>
       </c>
       <c r="F2076" t="n">
         <v>0.573215734857811</v>
@@ -49322,10 +49322,10 @@
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.489940436890507</v>
+        <v>-5.441261322110291</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.932112376108549</v>
+        <v>1.951584022020635</v>
       </c>
       <c r="F2077" t="n">
         <v>0.573215734857811</v>
@@ -49345,10 +49345,10 @@
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.500256535056859</v>
+        <v>-5.451577420276643</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.140890770120067</v>
+        <v>2.160362416032152</v>
       </c>
       <c r="F2078" t="n">
         <v>0.573215734857811</v>
@@ -49368,10 +49368,10 @@
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.500162567039486</v>
+        <v>-5.451483452259271</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.140107024239105</v>
+        <v>2.159578670151191</v>
       </c>
       <c r="F2079" t="n">
         <v>0.5735855962051289</v>
@@ -49391,10 +49391,10 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.648528794695631</v>
+        <v>-5.599849679915415</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.074992519121001</v>
+        <v>2.094464165033087</v>
       </c>
       <c r="F2080" t="n">
         <v>0.5735855962051289</v>
@@ -49414,10 +49414,10 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.647580371577592</v>
+        <v>-5.598901256797377</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.075371888368216</v>
+        <v>2.094843534280303</v>
       </c>
       <c r="F2081" t="n">
         <v>0.5735855962051289</v>
@@ -49437,10 +49437,10 @@
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.747850189536614</v>
+        <v>-5.699171074756398</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.0479915691657</v>
+        <v>2.067463215077786</v>
       </c>
       <c r="F2082" t="n">
         <v>0.5735855962051289</v>
@@ -49460,10 +49460,10 @@
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.741857942747802</v>
+        <v>-5.693178827967587</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.052334466305612</v>
+        <v>2.071806112217698</v>
       </c>
       <c r="F2083" t="n">
         <v>0.5735855962051289</v>
@@ -49483,10 +49483,10 @@
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.653299981617034</v>
+        <v>-5.604620866836819</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.081411786775688</v>
+        <v>2.100883432687775</v>
       </c>
       <c r="F2084" t="n">
         <v>0.5735855962051289</v>
@@ -49506,10 +49506,10 @@
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.63554090411396</v>
+        <v>-5.586861789333745</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.087824095215913</v>
+        <v>2.107295741128</v>
       </c>
       <c r="F2085" t="n">
         <v>0.5735855962051289</v>
@@ -49529,10 +49529,10 @@
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.535910753064893</v>
+        <v>-5.487231638284677</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.140458341544127</v>
+        <v>2.159929987456214</v>
       </c>
       <c r="F2086" t="n">
         <v>0.6732157472541964</v>
@@ -49552,10 +49552,10 @@
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.585310261753904</v>
+        <v>-5.536631146973688</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.309852803567249</v>
+        <v>2.329324449479336</v>
       </c>
       <c r="F2087" t="n">
         <v>0.6834745806859411</v>
@@ -49575,10 +49575,10 @@
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.378625788111528</v>
+        <v>-5.329946673331312</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.379715266127062</v>
+        <v>2.399186912039148</v>
       </c>
       <c r="F2088" t="n">
         <v>0.8901590543283168</v>
@@ -49598,10 +49598,10 @@
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.412782683109054</v>
+        <v>-5.364103568328838</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.368054021782156</v>
+        <v>2.387525667694243</v>
       </c>
       <c r="F2089" t="n">
         <v>0.8065752847875043</v>
@@ -49621,10 +49621,10 @@
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.320193204047597</v>
+        <v>-5.271514089267382</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.758586927396407</v>
+        <v>2.778058573308492</v>
       </c>
       <c r="F2090" t="n">
         <v>0.8065752847875043</v>
@@ -49644,10 +49644,10 @@
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.393353807820742</v>
+        <v>-5.344674693040527</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.733885797454251</v>
+        <v>2.753357443366338</v>
       </c>
       <c r="F2091" t="n">
         <v>0.7785540847532613</v>
@@ -49667,10 +49667,10 @@
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.3411374980244</v>
+        <v>-5.292458383244185</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.804602262696316</v>
+        <v>2.824073908608402</v>
       </c>
       <c r="F2092" t="n">
         <v>0.7785540847532613</v>
@@ -49690,10 +49690,10 @@
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.358803451984196</v>
+        <v>-5.31012433720398</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.806349851322409</v>
+        <v>2.825821497234495</v>
       </c>
       <c r="F2093" t="n">
         <v>0.7608881307934654</v>
@@ -49713,10 +49713,10 @@
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.373558776184336</v>
+        <v>-5.324879661404121</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.796085305681549</v>
+        <v>2.815556951593635</v>
       </c>
       <c r="F2094" t="n">
         <v>0.7608881307934654</v>
@@ -49736,10 +49736,10 @@
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.324094152814425</v>
+        <v>-5.275415038034209</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.806795658445794</v>
+        <v>2.82626730435788</v>
       </c>
       <c r="F2095" t="n">
         <v>0.810352754163377</v>
@@ -49759,10 +49759,10 @@
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.160986160660809</v>
+        <v>-5.112307045880594</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.868446523022175</v>
+        <v>2.887918168934261</v>
       </c>
       <c r="F2096" t="n">
         <v>0.9734607463169923</v>
@@ -49782,10 +49782,10 @@
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.028178535163643</v>
+        <v>-4.979499420383427</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.930616609912169</v>
+        <v>2.950088255824255</v>
       </c>
       <c r="F2097" t="n">
         <v>0.9734607463169923</v>
@@ -49805,10 +49805,10 @@
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.090886451638201</v>
+        <v>-5.042207336857985</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.906390908308468</v>
+        <v>2.925862554220554</v>
       </c>
       <c r="F2098" t="n">
         <v>0.9107528298424346</v>
@@ -49828,10 +49828,10 @@
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.042878327794508</v>
+        <v>-4.994199213014292</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.888503574636297</v>
+        <v>2.907975220548383</v>
       </c>
       <c r="F2099" t="n">
         <v>0.9107528298424346</v>
@@ -49851,10 +49851,10 @@
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.964052670610918</v>
+        <v>-4.915373555830702</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.923966091067683</v>
+        <v>2.94343773697977</v>
       </c>
       <c r="F2100" t="n">
         <v>0.9895784870260251</v>
@@ -49874,10 +49874,10 @@
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.772117869357044</v>
+        <v>-4.723438754576828</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.99563910417627</v>
+        <v>3.015110750088356</v>
       </c>
       <c r="F2101" t="n">
         <v>0.9895784870260251</v>
@@ -49897,10 +49897,10 @@
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.653944491339116</v>
+        <v>-4.605265376558901</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.038262364772536</v>
+        <v>3.057734010684622</v>
       </c>
       <c r="F2102" t="n">
         <v>1.107751865043952</v>
@@ -49920,10 +49920,10 @@
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.540529808556385</v>
+        <v>-4.491850693776169</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.112716830748655</v>
+        <v>3.132188476660742</v>
       </c>
       <c r="F2103" t="n">
         <v>1.221166547826684</v>
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.762555340764562</v>
+        <v>3.875138663675258</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.91363342535514</v>
+        <v>5.064379215075297</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.540529808556385</v>
+        <v>-4.491850693776169</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.112716830748655</v>
+        <v>3.132188476660742</v>
       </c>
       <c r="F2104" t="n">
         <v>1.221166547826684</v>
       </c>
       <c r="G2104" t="n">
-        <v>4.906697222341508</v>
+        <v>5.057443012061665</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241001.xlsx
+++ b/tame_output/ON/bt/strategyON_20241001.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>48.4%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>118.8%</t>
+          <t>112.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>99.9%</t>
+          <t>94.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>194.8%</t>
+          <t>177.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.8%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-72.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.3%</t>
+          <t>420.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-610.8%</t>
+          <t>-617.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-34.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-63.0%</t>
+          <t>-65.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.6%</t>
+          <t>-204.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-101.9%</t>
+          <t>-100.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
     </row>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121464</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
         <v>3.561451189754754</v>
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906077</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.835613200460291</v>
+        <v>-4.904539191551084</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.606686330994486</v>
+        <v>1.579115934558168</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.5449499618207787</v>
+        <v>0.508797365186741</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.868258012584818</v>
+        <v>3.846566454604395</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912982</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.780282612558528</v>
+        <v>-4.849208603649322</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.663785502767249</v>
+        <v>1.636215106330932</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.6002805497225409</v>
+        <v>0.5641279530885032</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.936423301937934</v>
+        <v>3.91473174395751</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.768228485645565</v>
+        <v>-4.837154476736359</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.662293721433872</v>
+        <v>1.634723324997555</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.6123346766355037</v>
+        <v>0.576182080001466</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.937342345987148</v>
+        <v>3.915650788006726</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.809383605213786</v>
+        <v>-4.87830959630458</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.64771230379072</v>
+        <v>1.620141907354402</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5711795570672827</v>
+        <v>0.535026960433245</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.914529904430352</v>
+        <v>3.892838346449929</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.741335042522256</v>
+        <v>-4.81026103361305</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.687782754745214</v>
+        <v>1.660212358308897</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6392281197588126</v>
+        <v>0.6030755231247749</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.968210067923152</v>
+        <v>3.94651850994273</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013422</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.972935435691757</v>
+        <v>-5.041861426782551</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.615345267651008</v>
+        <v>1.587774871214691</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6392281197588126</v>
+        <v>0.6030755231247749</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.988412738096747</v>
+        <v>3.966721180116324</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498967</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.022986981220976</v>
+        <v>-5.09191297231177</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.578930885506202</v>
+        <v>1.551360489069885</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6392281197588126</v>
+        <v>0.6030755231247749</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.972018974163628</v>
+        <v>3.950327416183206</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.198093813797421</v>
+        <v>-5.267019804888214</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.469140066069091</v>
+        <v>1.441569669632774</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6392281197588126</v>
+        <v>0.6030755231247749</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.932270887757095</v>
+        <v>3.910579329776673</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.001993660366898</v>
+        <v>-5.070919651457691</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.55460274643824</v>
+        <v>1.527032350001923</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8353282731893354</v>
+        <v>0.7991756765552978</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.056953598812349</v>
+        <v>4.035262040831927</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.848968268253613</v>
+        <v>-4.917894259344407</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.714983902856459</v>
+        <v>1.687413506420141</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9883536653026196</v>
+        <v>0.9522010686685819</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.247939833653223</v>
+        <v>4.226248275672801</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.877275582126884</v>
+        <v>-4.946201573217677</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.891127202215443</v>
+        <v>1.863556805779126</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9883536653026196</v>
+        <v>0.9522010686685819</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.435406058561517</v>
+        <v>4.413714500581094</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.043868807240406</v>
+        <v>-5.112794798331199</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.793892863524117</v>
+        <v>1.766322467087799</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8217604401890972</v>
+        <v>0.7856078435550595</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.304853074847486</v>
+        <v>4.283161516867063</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.02083301387884</v>
+        <v>-5.089759004969634</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.806783583530461</v>
+        <v>1.779213187094144</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8217604401890972</v>
+        <v>0.7856078435550595</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.308529477509204</v>
+        <v>4.28683791952878</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.991587033423143</v>
+        <v>-5.060513024513937</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.816100030836235</v>
+        <v>1.788529634399918</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8217604401890972</v>
+        <v>0.7856078435550595</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.306147532632699</v>
+        <v>4.284455974652277</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.098512581300994</v>
+        <v>-5.167438572391788</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.77062305084273</v>
+        <v>1.743052654406412</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7148348923112459</v>
+        <v>0.6786822956772082</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.239285443063623</v>
+        <v>4.2175938850832</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.243531139808243</v>
+        <v>-5.312457130899037</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.714044429583064</v>
+        <v>1.686474033146747</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5698163338039973</v>
+        <v>0.5336637371699596</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.153703110102508</v>
+        <v>4.132011552122085</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.361872905592961</v>
+        <v>-5.430798896683754</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.76663896252693</v>
+        <v>1.739068566090613</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5805023723668874</v>
+        <v>0.5443497757328497</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.260045972497995</v>
+        <v>4.238354414517572</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.413283327913669</v>
+        <v>-5.482209319004462</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.743860490724586</v>
+        <v>1.716290094288269</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5805023723668874</v>
+        <v>0.5443497757328497</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.257831669623934</v>
+        <v>4.236140111643512</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.49270277912142</v>
+        <v>-5.561628770212214</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.711995838315775</v>
+        <v>1.684425441879457</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5805023723668874</v>
+        <v>0.5443497757328497</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.257734797698223</v>
+        <v>4.236043239717801</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.588165777038638</v>
+        <v>-5.657091768129431</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.673804532706931</v>
+        <v>1.646234136270613</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5805023723668874</v>
+        <v>0.5443497757328497</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.257728691256267</v>
+        <v>4.236037133275844</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217997</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.523789866187923</v>
+        <v>-5.592715857278717</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.697651293609827</v>
+        <v>1.67008089717351</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6448782832176025</v>
+        <v>0.6087256865835649</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.294450634329306</v>
+        <v>4.272759076348883</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.530479913539902</v>
+        <v>-5.64808501941091</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.700709092416762</v>
+        <v>1.653667050068359</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6448782832176025</v>
+        <v>0.6087256865835649</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.300184452077032</v>
+        <v>4.27849289409661</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113276</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.548698380537511</v>
+        <v>-5.666303486408519</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.692960068960651</v>
+        <v>1.645918026612248</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6197718459617604</v>
+        <v>0.5836192493277227</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.28465895306646</v>
+        <v>4.262967395086037</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.460491546389933</v>
+        <v>-5.578096652260941</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.748117195470001</v>
+        <v>1.701075153121598</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6197718459617604</v>
+        <v>0.5836192493277227</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.304533345916779</v>
+        <v>4.282841787936356</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.354456551184623</v>
+        <v>-5.472061657055631</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.774231894076852</v>
+        <v>1.727189851728449</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6197718459617604</v>
+        <v>0.5836192493277227</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.288234046441507</v>
+        <v>4.266542488461083</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.171244888051528</v>
+        <v>-5.288849993922536</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.849947508794136</v>
+        <v>1.802905466445733</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6197718459617604</v>
+        <v>0.5836192493277227</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.290664995905552</v>
+        <v>4.268973437925129</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.099523441037677</v>
+        <v>-5.217128546908685</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.861580493679054</v>
+        <v>1.81453845133065</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.691493292975611</v>
+        <v>0.6553406963415733</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.316642270193239</v>
+        <v>4.294950712212817</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.077150415429971</v>
+        <v>-5.194755521300979</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.817445449843308</v>
+        <v>1.770403407494904</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.7027490440885126</v>
+        <v>0.6665964474544749</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.270311466782152</v>
+        <v>4.24861990880173</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.110166711340716</v>
+        <v>-5.227771817211724</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.989437136364365</v>
+        <v>1.942395094015962</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6333116674217609</v>
+        <v>0.5971590707877232</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.413847245667457</v>
+        <v>4.392155687687034</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.098639075691107</v>
+        <v>-5.216244181562115</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.985969416452458</v>
+        <v>1.938927374104054</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6923123256231234</v>
+        <v>0.6561597289890857</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.441168866416523</v>
+        <v>4.4194773084361</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.195980577033476</v>
+        <v>-5.313585682904484</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.950700928437299</v>
+        <v>1.903658886088896</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.647892143457635</v>
+        <v>0.6117395468235973</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.418184869639019</v>
+        <v>4.396493311658596</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.70520107942768</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.281836606373442</v>
+        <v>-5.39944171224445</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.91760959889415</v>
+        <v>1.870567556545747</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6055160742315</v>
+        <v>0.5693634775974623</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.394010310296176</v>
+        <v>4.372318752315753</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610378</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.290673403789562</v>
+        <v>-5.40827850966057</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.896494081748205</v>
+        <v>1.849452039399802</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5980739015901493</v>
+        <v>0.5619213049561116</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.371964208531868</v>
+        <v>4.350272650551444</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667451</v>
+        <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.38205596635502</v>
+        <v>-5.499661072226028</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.870105567767071</v>
+        <v>1.823063525418668</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5615090168708046</v>
+        <v>0.5253564202367669</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.36018978874531</v>
+        <v>4.338498230764887</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889187</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.370349248368014</v>
+        <v>-5.487954354239022</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.976916512786141</v>
+        <v>1.929874470437738</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.573215734857811</v>
+        <v>0.5370631382237733</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.469342077361782</v>
+        <v>4.447650519381359</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409562</v>
+        <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.441261322110291</v>
+        <v>-5.5588664279813</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.951584022020635</v>
+        <v>1.904541979672232</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.573215734857811</v>
+        <v>0.5370631382237733</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.472374416093187</v>
+        <v>4.450682858112764</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452568</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.451577420276643</v>
+        <v>-5.569182526147652</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.160362416032152</v>
+        <v>2.113320373683749</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.573215734857811</v>
+        <v>0.5370631382237733</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.685279249371245</v>
+        <v>4.663587691390822</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762283</v>
+        <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.451483452259271</v>
+        <v>-5.56908855813028</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.159578670151191</v>
+        <v>2.112536627802788</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5735855962051289</v>
+        <v>0.5374329995710913</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.684679833091725</v>
+        <v>4.662988275111302</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988014</v>
+        <v>3.633213467988013</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.599849679915415</v>
+        <v>-5.717454785786424</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.094464165033087</v>
+        <v>2.047422122684683</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5735855962051289</v>
+        <v>0.5374329995710913</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.678911819036079</v>
+        <v>4.657220261055656</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740918</v>
+        <v>3.647907242740919</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.598901256797377</v>
+        <v>-5.716506362668386</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.094843534280303</v>
+        <v>2.047801491931899</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5735855962051289</v>
+        <v>0.5374329995710913</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.678911819036079</v>
+        <v>4.657220261055656</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663622</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.699171074756398</v>
+        <v>-5.816776180627407</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.067463215077786</v>
+        <v>2.020421172729383</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5735855962051289</v>
+        <v>0.5374329995710913</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.691639427017171</v>
+        <v>4.669947869036748</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.693178827967587</v>
+        <v>-5.810783933838596</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.071806112217698</v>
+        <v>2.024764069869295</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5735855962051289</v>
+        <v>0.5374329995710913</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.693585425441559</v>
+        <v>4.671893867461136</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149214</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.604620866836819</v>
+        <v>-5.722225972707828</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.100883432687775</v>
+        <v>2.053841390339371</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5735855962051289</v>
+        <v>0.5374329995710913</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.687239561459328</v>
+        <v>4.665548003478905</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383086</v>
+        <v>3.735300721383088</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.586861789333745</v>
+        <v>-5.704466895204754</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.107295741128</v>
+        <v>2.060253698779596</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5735855962051289</v>
+        <v>0.5374329995710913</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.686548238898324</v>
+        <v>4.6648566809179</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720992</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.487231638284677</v>
+        <v>-5.604836744155686</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.159929987456214</v>
+        <v>2.11288794510781</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6732157472541964</v>
+        <v>0.6370631506201587</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.759108515436351</v>
+        <v>4.737416957455928</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455267</v>
+        <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.536631146973688</v>
+        <v>-5.654236252844697</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.329324449479336</v>
+        <v>2.282282407130932</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6834745806859411</v>
+        <v>0.6473219840519034</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.954418080994124</v>
+        <v>4.932726523013701</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963128</v>
+        <v>3.749078058963129</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.329946673331312</v>
+        <v>-5.447551779202321</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.399186912039148</v>
+        <v>2.352144869690744</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8901590543283168</v>
+        <v>0.8540064576942791</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.065617438282411</v>
+        <v>5.043925880301988</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162538</v>
+        <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.364103568328838</v>
+        <v>-5.481708674199847</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.387525667694243</v>
+        <v>2.340483625345839</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.8065752847875043</v>
+        <v>0.7704226881534666</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.017468690212029</v>
+        <v>4.995777132231606</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652378</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.271514089267382</v>
+        <v>-5.389119195138391</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.778058573308492</v>
+        <v>2.731016530960089</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.8065752847875043</v>
+        <v>0.7704226881534666</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.370965804201696</v>
+        <v>5.349274246221274</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108668</v>
+        <v>3.80905590510867</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.344674693040527</v>
+        <v>-5.462279798911536</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.753357443366338</v>
+        <v>2.706315401017934</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7785540847532613</v>
+        <v>0.7424014881192236</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.358716195748253</v>
+        <v>5.337024637767831</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103559</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.292458383244185</v>
+        <v>-5.410063489115194</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.824073908608402</v>
+        <v>2.777031866259998</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7785540847532613</v>
+        <v>0.7424014881192236</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.408546137071781</v>
+        <v>5.386854579091358</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047741</v>
+        <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.31012433720398</v>
+        <v>-5.378165972029948</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.825821497234495</v>
+        <v>2.798604843304108</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7608881307934654</v>
+        <v>0.7742990052044694</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.406760534905914</v>
+        <v>5.414807059552516</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.324879661404121</v>
+        <v>-5.392921296230089</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.815556951593635</v>
+        <v>2.788340297663248</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7608881307934654</v>
+        <v>0.7742990052044694</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.402398118945111</v>
+        <v>5.410444643591713</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.275415038034209</v>
+        <v>-5.343456672860177</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.82626730435788</v>
+        <v>2.799050650427493</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.810352754163377</v>
+        <v>0.823763628574381</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.423001396383338</v>
+        <v>5.431047921029941</v>
       </c>
     </row>
     <row r="2096">
@@ -49759,16 +49759,16 @@
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.112307045880594</v>
+        <v>-5.180348680706562</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.887918168934261</v>
+        <v>2.860701515003873</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9734607463169923</v>
+        <v>0.9868716207279963</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.517273859390442</v>
+        <v>5.525320384037045</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844241</v>
+        <v>3.847096478844243</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.979499420383427</v>
+        <v>-5.047541055209395</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.950088255824255</v>
+        <v>2.922871601893868</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9734607463169923</v>
+        <v>0.9868716207279963</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.52632089608157</v>
+        <v>5.534367420728172</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790945</v>
+        <v>3.832425987790947</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.042207336857985</v>
+        <v>-5.110248971683953</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.925862554220554</v>
+        <v>2.898645900290167</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9107528298424346</v>
+        <v>0.9241637042534385</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.489553611182957</v>
+        <v>5.497600135829559</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578991</v>
+        <v>3.861579399578993</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.994199213014292</v>
+        <v>-5.06224084784026</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.907975220548383</v>
+        <v>2.880758566617996</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9107528298424346</v>
+        <v>0.9241637042534385</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.452463027973309</v>
+        <v>5.460509552619912</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629879</v>
+        <v>3.872253907629881</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.915373555830702</v>
+        <v>-4.98341519065667</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.94343773697977</v>
+        <v>2.916221083049383</v>
       </c>
       <c r="F2100" t="n">
-        <v>0.9895784870260251</v>
+        <v>1.002989361437029</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.503690675841414</v>
+        <v>5.511737200488017</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686402</v>
+        <v>3.868502531686404</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.723438754576828</v>
+        <v>-4.791480389402796</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.015110750088356</v>
+        <v>2.987894096157969</v>
       </c>
       <c r="F2101" t="n">
-        <v>0.9895784870260251</v>
+        <v>1.002989361437029</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.498589768448451</v>
+        <v>5.506636293095053</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.849324044046709</v>
+        <v>3.84932404404671</v>
       </c>
       <c r="C2102" t="n">
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.605265376558901</v>
+        <v>-4.673307011384869</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.057734010684622</v>
+        <v>3.030517356754235</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.107751865043952</v>
+        <v>1.121162739454956</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.564847704648303</v>
+        <v>5.572894229294905</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.836463274528998</v>
+        <v>3.836463274528999</v>
       </c>
       <c r="C2103" t="n">
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.491850693776169</v>
+        <v>-4.559892328602138</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.132188476660742</v>
+        <v>3.104971822730354</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.221166547826684</v>
+        <v>1.234577422237688</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.661985107180968</v>
+        <v>5.670031631827571</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.875138663675258</v>
+        <v>3.764284530967168</v>
       </c>
       <c r="C2104" t="n">
-        <v>5.064379215075297</v>
+        <v>4.893099557689079</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.491850693776169</v>
+        <v>-4.559892328602138</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.132188476660742</v>
+        <v>3.104971822730354</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.221166547826684</v>
+        <v>1.234577422237688</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.057443012061665</v>
+        <v>4.886163354675447</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241001.xlsx
+++ b/tame_output/ON/bt/strategyON_20241001.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>112.7%</t>
+          <t>114.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>94.9%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>177.7%</t>
+          <t>182.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.3%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-49.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-72.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.5%</t>
+          <t>421.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-617.6%</t>
+          <t>-610.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.6%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-65.7%</t>
+          <t>-63.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.8%</t>
+          <t>-205.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-100.5%</t>
+          <t>-98.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.9%</t>
         </is>
       </c>
     </row>
@@ -48517,16 +48517,16 @@
         <v>3.54128803549235</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.904539191551084</v>
+        <v>-4.835613200460291</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.579115934558168</v>
+        <v>1.606686330994486</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.508797365186741</v>
+        <v>0.5449499618207787</v>
       </c>
       <c r="G2042" t="n">
-        <v>3.846566454604395</v>
+        <v>3.868258012584818</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.849208603649322</v>
+        <v>-4.802154655694588</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.636215106330932</v>
+        <v>1.655036685512825</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.5641279530885032</v>
+        <v>0.578408506586481</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.91473174395751</v>
+        <v>3.923300076056297</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.837154476736359</v>
+        <v>-4.790100528781625</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.634723324997555</v>
+        <v>1.653544904179448</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.576182080001466</v>
+        <v>0.5904626334994438</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.915650788006726</v>
+        <v>3.924219120105513</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.87830959630458</v>
+        <v>-4.831255648349846</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.620141907354402</v>
+        <v>1.638963486536296</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.535026960433245</v>
+        <v>0.5493075139312229</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.892838346449929</v>
+        <v>3.901406678548716</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.81026103361305</v>
+        <v>-4.763207085658316</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.660212358308897</v>
+        <v>1.67903393749079</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6030755231247749</v>
+        <v>0.6173560766227527</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.94651850994273</v>
+        <v>3.955086842041516</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.041861426782551</v>
+        <v>-4.994807478827817</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.587774871214691</v>
+        <v>1.606596450396584</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6030755231247749</v>
+        <v>0.6173560766227527</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.966721180116324</v>
+        <v>3.97528951221511</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498966</v>
+        <v>3.666747201498967</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.09191297231177</v>
+        <v>-5.044859024357036</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.551360489069885</v>
+        <v>1.570182068251778</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6030755231247749</v>
+        <v>0.6173560766227527</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.950327416183206</v>
+        <v>3.958895748281993</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.267019804888214</v>
+        <v>-5.219965856933481</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.441569669632774</v>
+        <v>1.460391248814667</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6030755231247749</v>
+        <v>0.6173560766227527</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.910579329776673</v>
+        <v>3.919147661875459</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.070919651457691</v>
+        <v>-5.023865703502958</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.527032350001923</v>
+        <v>1.545853929183816</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7991756765552978</v>
+        <v>0.8134562300532756</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.035262040831927</v>
+        <v>4.043830372930713</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.917894259344407</v>
+        <v>-4.870840311389673</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.687413506420141</v>
+        <v>1.706235085602035</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9522010686685819</v>
+        <v>0.9664816221665598</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.226248275672801</v>
+        <v>4.234816607771588</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.946201573217677</v>
+        <v>-4.899147625262944</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.863556805779126</v>
+        <v>1.882378384961019</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9522010686685819</v>
+        <v>0.9664816221665598</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.413714500581094</v>
+        <v>4.422282832679881</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.112794798331199</v>
+        <v>-5.065740850376466</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.766322467087799</v>
+        <v>1.785144046269693</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7856078435550595</v>
+        <v>0.7998883970530373</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.283161516867063</v>
+        <v>4.29172984896585</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.089759004969634</v>
+        <v>-5.0427050570149</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.779213187094144</v>
+        <v>1.798034766276037</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7856078435550595</v>
+        <v>0.7998883970530373</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.28683791952878</v>
+        <v>4.295406251627568</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.060513024513937</v>
+        <v>-5.013459076559204</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.788529634399918</v>
+        <v>1.807351213581811</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7856078435550595</v>
+        <v>0.7998883970530373</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.284455974652277</v>
+        <v>4.293024306751063</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.167438572391788</v>
+        <v>-5.120384624437055</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.743052654406412</v>
+        <v>1.761874233588305</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6786822956772082</v>
+        <v>0.6929628491751859</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.2175938850832</v>
+        <v>4.226162217181987</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.312457130899037</v>
+        <v>-5.265403182944303</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.686474033146747</v>
+        <v>1.70529561232864</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5336637371699596</v>
+        <v>0.5479442906679374</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.132011552122085</v>
+        <v>4.140579884220872</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.430798896683754</v>
+        <v>-5.383744948729021</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.739068566090613</v>
+        <v>1.757890145272506</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5443497757328497</v>
+        <v>0.5586303292308274</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.238354414517572</v>
+        <v>4.246922746616359</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.482209319004462</v>
+        <v>-5.435155371049729</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.716290094288269</v>
+        <v>1.735111673470162</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5443497757328497</v>
+        <v>0.5586303292308274</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.236140111643512</v>
+        <v>4.244708443742298</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.561628770212214</v>
+        <v>-5.51457482225748</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.684425441879457</v>
+        <v>1.703247021061351</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5443497757328497</v>
+        <v>0.5586303292308274</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.236043239717801</v>
+        <v>4.244611571816588</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.657091768129431</v>
+        <v>-5.610037820174698</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.646234136270613</v>
+        <v>1.665055715452506</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5443497757328497</v>
+        <v>0.5586303292308274</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.236037133275844</v>
+        <v>4.24460546537463</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.592715857278717</v>
+        <v>-5.545661909323983</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.67008089717351</v>
+        <v>1.688902476355403</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6087256865835649</v>
+        <v>0.6230062400815426</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.272759076348883</v>
+        <v>4.28132740844767</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.64808501941091</v>
+        <v>-5.601031071456177</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.653667050068359</v>
+        <v>1.672488629250252</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6087256865835649</v>
+        <v>0.6230062400815426</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.27849289409661</v>
+        <v>4.287061226195397</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.666303486408519</v>
+        <v>-5.619249538453785</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.645918026612248</v>
+        <v>1.664739605794141</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5836192493277227</v>
+        <v>0.5978998028257004</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.262967395086037</v>
+        <v>4.271535727184824</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.578096652260941</v>
+        <v>-5.531042704306207</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.701075153121598</v>
+        <v>1.719896732303491</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5836192493277227</v>
+        <v>0.5978998028257004</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.282841787936356</v>
+        <v>4.291410120035143</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016436</v>
+        <v>3.794486844016437</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.472061657055631</v>
+        <v>-5.425007709100898</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.727189851728449</v>
+        <v>1.746011430910343</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5836192493277227</v>
+        <v>0.5978998028257004</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.266542488461083</v>
+        <v>4.27511082055987</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307668</v>
+        <v>3.794705093307669</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.288849993922536</v>
+        <v>-5.241796045967803</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.802905466445733</v>
+        <v>1.821727045627626</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5836192493277227</v>
+        <v>0.5978998028257004</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.268973437925129</v>
+        <v>4.277541770023916</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863549</v>
+        <v>3.77684655786355</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.217128546908685</v>
+        <v>-5.170074598953952</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.81453845133065</v>
+        <v>1.833360030512544</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6553406963415733</v>
+        <v>0.6696212498395511</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.294950712212817</v>
+        <v>4.303519044311603</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394109</v>
+        <v>3.72378970539411</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.194755521300979</v>
+        <v>-5.147701573346246</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.770403407494904</v>
+        <v>1.789224986676798</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6665964474544749</v>
+        <v>0.6808770009524526</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.24861990880173</v>
+        <v>4.257188240900516</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456726</v>
+        <v>3.715607446456727</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.227771817211724</v>
+        <v>-5.18071786925699</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.942395094015962</v>
+        <v>1.961216673197856</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5971590707877232</v>
+        <v>0.611439624285701</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.392155687687034</v>
+        <v>4.40072401978582</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.216244181562115</v>
+        <v>-5.169190233607382</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.938927374104054</v>
+        <v>1.957748953285948</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6561597289890857</v>
+        <v>0.6704402824870634</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.4194773084361</v>
+        <v>4.428045640534887</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.313585682904484</v>
+        <v>-5.26653173494975</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.903658886088896</v>
+        <v>1.922480465270789</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6117395468235973</v>
+        <v>0.6260201003215751</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.396493311658596</v>
+        <v>4.405061643757382</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.39944171224445</v>
+        <v>-5.330814847229837</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.870567556545747</v>
+        <v>1.898018302551593</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5693634775974623</v>
+        <v>0.5948088654849599</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.372318752315753</v>
+        <v>4.387585985048251</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.40827850966057</v>
+        <v>-5.339651644645956</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.849452039399802</v>
+        <v>1.876902785405647</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5619213049561116</v>
+        <v>0.5873666928436092</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.350272650551444</v>
+        <v>4.365539883283943</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.499661072226028</v>
+        <v>-5.431034207211415</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.823063525418668</v>
+        <v>1.850514271424513</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5253564202367669</v>
+        <v>0.5508018081242645</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.338498230764887</v>
+        <v>4.353765463497385</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.487954354239022</v>
+        <v>-5.419327489224409</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.929874470437738</v>
+        <v>1.957325216443583</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5370631382237733</v>
+        <v>0.5625085261112709</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.447650519381359</v>
+        <v>4.462917752113857</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.5588664279813</v>
+        <v>-5.490239562966686</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.904541979672232</v>
+        <v>1.931992725678077</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5370631382237733</v>
+        <v>0.5625085261112709</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.450682858112764</v>
+        <v>4.465950090845262</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.569182526147652</v>
+        <v>-5.500555661133038</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.113320373683749</v>
+        <v>2.140771119689595</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5370631382237733</v>
+        <v>0.5625085261112709</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.663587691390822</v>
+        <v>4.67885492412332</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.56908855813028</v>
+        <v>-5.500461693115665</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.112536627802788</v>
+        <v>2.139987373808633</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5374329995710913</v>
+        <v>0.5628783874585889</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.662988275111302</v>
+        <v>4.678255507843801</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.717454785786424</v>
+        <v>-5.64882792077181</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.047422122684683</v>
+        <v>2.074872868690529</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5374329995710913</v>
+        <v>0.5628783874585889</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.657220261055656</v>
+        <v>4.672487493788155</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740919</v>
+        <v>3.64790724274092</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.716506362668386</v>
+        <v>-5.647879497653771</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.047801491931899</v>
+        <v>2.075252237937745</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5374329995710913</v>
+        <v>0.5628783874585889</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.657220261055656</v>
+        <v>4.672487493788155</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.816776180627407</v>
+        <v>-5.748149315612793</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.020421172729383</v>
+        <v>2.047871918735229</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5374329995710913</v>
+        <v>0.5628783874585889</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.669947869036748</v>
+        <v>4.685215101769247</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424766</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.810783933838596</v>
+        <v>-5.742157068823981</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.024764069869295</v>
+        <v>2.052214815875141</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5374329995710913</v>
+        <v>0.5628783874585889</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.671893867461136</v>
+        <v>4.687161100193634</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.722225972707828</v>
+        <v>-5.653599107693213</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.053841390339371</v>
+        <v>2.081292136345217</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5374329995710913</v>
+        <v>0.5628783874585889</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.665548003478905</v>
+        <v>4.680815236211403</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.704466895204754</v>
+        <v>-5.635840030190139</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.060253698779596</v>
+        <v>2.087704444785442</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5374329995710913</v>
+        <v>0.5628783874585889</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.6648566809179</v>
+        <v>4.680123913650399</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.604836744155686</v>
+        <v>-5.536209879141071</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.11288794510781</v>
+        <v>2.140338691113656</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6370631506201587</v>
+        <v>0.6625085385076563</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.737416957455928</v>
+        <v>4.752684190188426</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.654236252844697</v>
+        <v>-5.585609387830083</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.282282407130932</v>
+        <v>2.309733153136778</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6473219840519034</v>
+        <v>0.6727673719394011</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.932726523013701</v>
+        <v>4.947993755746199</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.447551779202321</v>
+        <v>-5.378924914187706</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.352144869690744</v>
+        <v>2.37959561569659</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8540064576942791</v>
+        <v>0.8794518455817767</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.043925880301988</v>
+        <v>5.059193113034487</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.481708674199847</v>
+        <v>-5.413081809185233</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.340483625345839</v>
+        <v>2.367934371351685</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7704226881534666</v>
+        <v>0.7958680760409642</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.995777132231606</v>
+        <v>5.011044364964104</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.389119195138391</v>
+        <v>-5.320492330123776</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.731016530960089</v>
+        <v>2.758467276965935</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7704226881534666</v>
+        <v>0.7958680760409642</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.349274246221274</v>
+        <v>5.364541478953772</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.462279798911536</v>
+        <v>-5.393652933896921</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.706315401017934</v>
+        <v>2.73376614702378</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7424014881192236</v>
+        <v>0.7678468760067212</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.337024637767831</v>
+        <v>5.35229187050033</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.410063489115194</v>
+        <v>-5.341436624100579</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.777031866259998</v>
+        <v>2.804482612265844</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7424014881192236</v>
+        <v>0.7678468760067212</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.386854579091358</v>
+        <v>5.402121811823857</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.378165972029948</v>
+        <v>-5.309539107015333</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.798604843304108</v>
+        <v>2.826055589309953</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7742990052044694</v>
+        <v>0.799744393091967</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.414807059552516</v>
+        <v>5.430074292285015</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.392921296230089</v>
+        <v>-5.324294431215474</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.788340297663248</v>
+        <v>2.815791043669094</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7742990052044694</v>
+        <v>0.799744393091967</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.410444643591713</v>
+        <v>5.425711876324212</v>
       </c>
     </row>
     <row r="2095">
@@ -49736,16 +49736,16 @@
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.343456672860177</v>
+        <v>-5.274829807845562</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.799050650427493</v>
+        <v>2.826501396433339</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.823763628574381</v>
+        <v>0.8492090164618786</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.431047921029941</v>
+        <v>5.446315153762439</v>
       </c>
     </row>
     <row r="2096">
@@ -49759,16 +49759,16 @@
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.180348680706562</v>
+        <v>-5.111721815691947</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.860701515003873</v>
+        <v>2.888152261009719</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9868716207279963</v>
+        <v>1.012317008615494</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.525320384037045</v>
+        <v>5.540587616769542</v>
       </c>
     </row>
     <row r="2097">
@@ -49782,16 +49782,16 @@
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.047541055209395</v>
+        <v>-4.97891419019478</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.922871601893868</v>
+        <v>2.950322347899714</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9868716207279963</v>
+        <v>1.012317008615494</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.534367420728172</v>
+        <v>5.549634653460671</v>
       </c>
     </row>
     <row r="2098">
@@ -49805,16 +49805,16 @@
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.110248971683953</v>
+        <v>-5.041622106669339</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.898645900290167</v>
+        <v>2.926096646296013</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9241637042534385</v>
+        <v>0.9496090921409363</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.497600135829559</v>
+        <v>5.512867368562058</v>
       </c>
     </row>
     <row r="2099">
@@ -49828,16 +49828,16 @@
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.06224084784026</v>
+        <v>-4.993613982825646</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.880758566617996</v>
+        <v>2.908209312623842</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9241637042534385</v>
+        <v>0.9496090921409363</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.460509552619912</v>
+        <v>5.47577678535241</v>
       </c>
     </row>
     <row r="2100">
@@ -49851,16 +49851,16 @@
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.98341519065667</v>
+        <v>-4.914788325642055</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.916221083049383</v>
+        <v>2.943671829055228</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.002989361437029</v>
+        <v>1.028434749324527</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.511737200488017</v>
+        <v>5.527004433220515</v>
       </c>
     </row>
     <row r="2101">
@@ -49874,16 +49874,16 @@
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.791480389402796</v>
+        <v>-4.722853524388182</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.987894096157969</v>
+        <v>3.015344842163815</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.002989361437029</v>
+        <v>1.028434749324527</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.506636293095053</v>
+        <v>5.521903525827552</v>
       </c>
     </row>
     <row r="2102">
@@ -49897,16 +49897,16 @@
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.673307011384869</v>
+        <v>-4.604680146370255</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.030517356754235</v>
+        <v>3.057968102760081</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.121162739454956</v>
+        <v>1.146608127342454</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.572894229294905</v>
+        <v>5.588161462027403</v>
       </c>
     </row>
     <row r="2103">
@@ -49920,16 +49920,16 @@
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.559892328602138</v>
+        <v>-4.491265463587523</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.104971822730354</v>
+        <v>3.1324225687362</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.234577422237688</v>
+        <v>1.260022810125185</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.670031631827571</v>
+        <v>5.685298864560069</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.764284530967168</v>
+        <v>3.796172938801832</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.893099557689079</v>
+        <v>4.936235903995918</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.559892328602138</v>
+        <v>-4.491265463587523</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.104971822730354</v>
+        <v>3.1324225687362</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.234577422237688</v>
+        <v>1.260022810125185</v>
       </c>
       <c r="G2104" t="n">
-        <v>4.886163354675447</v>
+        <v>4.929299700982286</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241001.xlsx
+++ b/tame_output/ON/bt/strategyON_20241001.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>52.1%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>114.3%</t>
+          <t>113.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>182.0%</t>
+          <t>179.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-37.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.0%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-72.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.4%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.0%</t>
+          <t>420.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-610.7%</t>
+          <t>-615.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-63.0%</t>
+          <t>-67.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-205.1%</t>
+          <t>-204.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-98.0%</t>
+          <t>-101.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>124.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-19.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>112.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>118.1%</t>
         </is>
       </c>
     </row>
@@ -48540,16 +48540,16 @@
         <v>3.576254972104409</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.802154655694588</v>
+        <v>-4.780282612558528</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.655036685512825</v>
+        <v>1.663785502767249</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.578408506586481</v>
+        <v>0.6002805497225409</v>
       </c>
       <c r="G2043" t="n">
-        <v>3.923300076056297</v>
+        <v>3.936423301937934</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.74376795653989</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.790100528781625</v>
+        <v>-4.847178123441527</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.653544904179448</v>
+        <v>1.630713866315488</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5904626334994438</v>
+        <v>0.5333850388395425</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.924219120105513</v>
+        <v>3.889972563309572</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811004</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.831255648349846</v>
+        <v>-4.888333243009748</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.638963486536296</v>
+        <v>1.616132448672335</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.5493075139312229</v>
+        <v>0.4922299192713215</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.901406678548716</v>
+        <v>3.867160121752775</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382915</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.763207085658316</v>
+        <v>-4.820284680318218</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.67903393749079</v>
+        <v>1.656202899626829</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.6173560766227527</v>
+        <v>0.5602784819628513</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.955086842041516</v>
+        <v>3.920840285245576</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013422</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.994807478827817</v>
+        <v>-5.051885073487719</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.606596450396584</v>
+        <v>1.583765412532623</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.6173560766227527</v>
+        <v>0.5602784819628513</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.97528951221511</v>
+        <v>3.94104295541917</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.044859024357036</v>
+        <v>-5.101936619016938</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.570182068251778</v>
+        <v>1.547351030387818</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.6173560766227527</v>
+        <v>0.5602784819628513</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.958895748281993</v>
+        <v>3.924649191486052</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800096</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.219965856933481</v>
+        <v>-5.277043451593382</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.460391248814667</v>
+        <v>1.437560210950707</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.6173560766227527</v>
+        <v>0.5602784819628513</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.919147661875459</v>
+        <v>3.884901105079519</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.023865703502958</v>
+        <v>-5.080943298162859</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.545853929183816</v>
+        <v>1.523022891319856</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8134562300532756</v>
+        <v>0.7563786353933742</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.043830372930713</v>
+        <v>4.009583816134772</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395085</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.870840311389673</v>
+        <v>-4.927917906049575</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.706235085602035</v>
+        <v>1.683404047738074</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9664816221665598</v>
+        <v>0.9094040275066584</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.234816607771588</v>
+        <v>4.200570050975648</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791147</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.899147625262944</v>
+        <v>-4.956225219922845</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.882378384961019</v>
+        <v>1.859547347097058</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9664816221665598</v>
+        <v>0.9094040275066584</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.422282832679881</v>
+        <v>4.388036275883939</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620433</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.065740850376466</v>
+        <v>-5.122818445036367</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.785144046269693</v>
+        <v>1.762313008405732</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7998883970530373</v>
+        <v>0.7428108023931359</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.29172984896585</v>
+        <v>4.257483292169909</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.0427050570149</v>
+        <v>-5.099782651674801</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.798034766276037</v>
+        <v>1.775203728412076</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7998883970530373</v>
+        <v>0.7428108023931359</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.295406251627568</v>
+        <v>4.261159694831627</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399467</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.013459076559204</v>
+        <v>-5.070536671219105</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.807351213581811</v>
+        <v>1.78452017571785</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7998883970530373</v>
+        <v>0.7428108023931359</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.293024306751063</v>
+        <v>4.258777749955122</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256368</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.120384624437055</v>
+        <v>-5.177462219096956</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.761874233588305</v>
+        <v>1.739043195724345</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6929628491751859</v>
+        <v>0.6358852545152845</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.226162217181987</v>
+        <v>4.191915660386046</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700998</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.265403182944303</v>
+        <v>-5.322480777604205</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.70529561232864</v>
+        <v>1.68246457446468</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.5479442906679374</v>
+        <v>0.490866696008036</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.140579884220872</v>
+        <v>4.106333327424931</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.71185242968701</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.383744948729021</v>
+        <v>-5.440822543388922</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.757890145272506</v>
+        <v>1.735059107408546</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5586303292308274</v>
+        <v>0.5015527345709261</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.246922746616359</v>
+        <v>4.212676189820418</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.7148790517908</v>
+        <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.435155371049729</v>
+        <v>-5.49223296570963</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.735111673470162</v>
+        <v>1.712280635606202</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5586303292308274</v>
+        <v>0.5015527345709261</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.244708443742298</v>
+        <v>4.210461886946358</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.70475794943733</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.51457482225748</v>
+        <v>-5.571652416917382</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.703247021061351</v>
+        <v>1.68041598319739</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5586303292308274</v>
+        <v>0.5015527345709261</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.244611571816588</v>
+        <v>4.210365015020646</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298394</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.610037820174698</v>
+        <v>-5.667115414834599</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.665055715452506</v>
+        <v>1.642224677588546</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5586303292308274</v>
+        <v>0.5015527345709261</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.24460546537463</v>
+        <v>4.21035890857869</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217996</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.545661909323983</v>
+        <v>-5.602739503983885</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.688902476355403</v>
+        <v>1.666071438491442</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6230062400815426</v>
+        <v>0.5659286454216412</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.28132740844767</v>
+        <v>4.247080851651729</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353532</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.601031071456177</v>
+        <v>-5.658108666116078</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.672488629250252</v>
+        <v>1.649657591386292</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6230062400815426</v>
+        <v>0.5659286454216412</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.287061226195397</v>
+        <v>4.252814669399456</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113275</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.619249538453785</v>
+        <v>-5.676327133113687</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.664739605794141</v>
+        <v>1.641908567930181</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5978998028257004</v>
+        <v>0.5408222081657991</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.271535727184824</v>
+        <v>4.237289170388883</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113684</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.531042704306207</v>
+        <v>-5.588120298966109</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.719896732303491</v>
+        <v>1.697065694439531</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5978998028257004</v>
+        <v>0.5408222081657991</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.291410120035143</v>
+        <v>4.257163563239201</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016437</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.425007709100898</v>
+        <v>-5.482085303760799</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.746011430910343</v>
+        <v>1.723180393046382</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5978998028257004</v>
+        <v>0.5408222081657991</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.27511082055987</v>
+        <v>4.24086426376393</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307669</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.241796045967803</v>
+        <v>-5.298873640627704</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.821727045627626</v>
+        <v>1.798896007763666</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5978998028257004</v>
+        <v>0.5408222081657991</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.277541770023916</v>
+        <v>4.243295213227976</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.77684655786355</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.170074598953952</v>
+        <v>-5.227152193613853</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.833360030512544</v>
+        <v>1.810528992648583</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6696212498395511</v>
+        <v>0.6125436551796497</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.303519044311603</v>
+        <v>4.269272487515662</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.72378970539411</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.147701573346246</v>
+        <v>-5.204779168006147</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.789224986676798</v>
+        <v>1.766393948812838</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6808770009524526</v>
+        <v>0.6237994062925513</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.257188240900516</v>
+        <v>4.222941684104575</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456727</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.18071786925699</v>
+        <v>-5.237795463916892</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.961216673197856</v>
+        <v>1.938385635333895</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.611439624285701</v>
+        <v>0.5543620296257996</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.40072401978582</v>
+        <v>4.36647746298988</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883676</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.169190233607382</v>
+        <v>-5.226267828267283</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.957748953285948</v>
+        <v>1.934917915421988</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6704402824870634</v>
+        <v>0.6133626878271621</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.428045640534887</v>
+        <v>4.393799083738946</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236294</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.26653173494975</v>
+        <v>-5.323609329609652</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.922480465270789</v>
+        <v>1.899649427406829</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6260201003215751</v>
+        <v>0.5689425056616737</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.405061643757382</v>
+        <v>4.370815086961442</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.70520107942768</v>
+        <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.330814847229837</v>
+        <v>-5.409465358949618</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.898018302551593</v>
+        <v>1.86655809786368</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5948088654849599</v>
+        <v>0.5265664364355387</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.387585985048251</v>
+        <v>4.346640527618599</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610379</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.339651644645956</v>
+        <v>-5.418302156365738</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.876902785405647</v>
+        <v>1.845442580717734</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5873666928436092</v>
+        <v>0.519124263794188</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.365539883283943</v>
+        <v>4.32459442585429</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667452</v>
+        <v>3.715544411667453</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.431034207211415</v>
+        <v>-5.509684718931196</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.850514271424513</v>
+        <v>1.8190540667366</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5508018081242645</v>
+        <v>0.4825593790748433</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.353765463497385</v>
+        <v>4.312820006067733</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889187</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.419327489224409</v>
+        <v>-5.49797800094419</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.957325216443583</v>
+        <v>1.925865011755671</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.5625085261112709</v>
+        <v>0.4942660970618498</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.462917752113857</v>
+        <v>4.421972294684205</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409563</v>
+        <v>3.682476099409565</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.490239562966686</v>
+        <v>-5.568890074686468</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.931992725678077</v>
+        <v>1.900532520990164</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.5625085261112709</v>
+        <v>0.4942660970618498</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.465950090845262</v>
+        <v>4.42500463341561</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452569</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.500555661133038</v>
+        <v>-5.57920617285282</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.140771119689595</v>
+        <v>2.109310915001682</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.5625085261112709</v>
+        <v>0.4942660970618498</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.67885492412332</v>
+        <v>4.637909466693668</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762282</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.500461693115665</v>
+        <v>-5.579112204835448</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.139987373808633</v>
+        <v>2.108527169120721</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.5628783874585889</v>
+        <v>0.4946359584091677</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.678255507843801</v>
+        <v>4.637310050414149</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988013</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.64882792077181</v>
+        <v>-5.727478432491592</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.074872868690529</v>
+        <v>2.043412664002616</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.5628783874585889</v>
+        <v>0.4946359584091677</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.672487493788155</v>
+        <v>4.631542036358502</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.64790724274092</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.647879497653771</v>
+        <v>-5.726530009373554</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.075252237937745</v>
+        <v>2.043792033249832</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.5628783874585889</v>
+        <v>0.4946359584091677</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.672487493788155</v>
+        <v>4.631542036358502</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663624</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.748149315612793</v>
+        <v>-5.826799827332575</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.047871918735229</v>
+        <v>2.016411714047315</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.5628783874585889</v>
+        <v>0.4946359584091677</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.685215101769247</v>
+        <v>4.644269644339595</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424768</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.742157068823981</v>
+        <v>-5.820807580543764</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.052214815875141</v>
+        <v>2.020754611187228</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.5628783874585889</v>
+        <v>0.4946359584091677</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.687161100193634</v>
+        <v>4.646215642763982</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.653599107693213</v>
+        <v>-5.732249619412996</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.081292136345217</v>
+        <v>2.049831931657303</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.5628783874585889</v>
+        <v>0.4946359584091677</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.680815236211403</v>
+        <v>4.639869778781751</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383088</v>
+        <v>3.73530072138309</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.635840030190139</v>
+        <v>-5.714490541909922</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.087704444785442</v>
+        <v>2.056244240097529</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.5628783874585889</v>
+        <v>0.4946359584091677</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.680123913650399</v>
+        <v>4.639178456220747</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720994</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.536209879141071</v>
+        <v>-5.614860390860854</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.140338691113656</v>
+        <v>2.108878486425743</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.6625085385076563</v>
+        <v>0.5942661094582352</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.752684190188426</v>
+        <v>4.711738732758774</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455268</v>
+        <v>3.77535709745527</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.585609387830083</v>
+        <v>-5.664259899549865</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.309733153136778</v>
+        <v>2.278272948448865</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6727673719394011</v>
+        <v>0.6045249428899799</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.947993755746199</v>
+        <v>4.907048298316547</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963129</v>
+        <v>3.749078058963131</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.378924914187706</v>
+        <v>-5.457575425907489</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.37959561569659</v>
+        <v>2.348135411008677</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8794518455817767</v>
+        <v>0.8112094165323556</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.059193113034487</v>
+        <v>5.018247655604834</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162539</v>
+        <v>3.740284389162541</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.413081809185233</v>
+        <v>-5.491732320905015</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.367934371351685</v>
+        <v>2.336474166663772</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7958680760409642</v>
+        <v>0.7276256469915431</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.011044364964104</v>
+        <v>4.970098907534452</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.320492330123776</v>
+        <v>-5.399142841843559</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.758467276965935</v>
+        <v>2.727007072278022</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7958680760409642</v>
+        <v>0.7276256469915431</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.364541478953772</v>
+        <v>5.32359602152412</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.80905590510867</v>
+        <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.393652933896921</v>
+        <v>-5.472303445616704</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.73376614702378</v>
+        <v>2.702305942335867</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.7678468760067212</v>
+        <v>0.6996044469573</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.35229187050033</v>
+        <v>5.311346413070677</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.835202441103562</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.341436624100579</v>
+        <v>-5.420087135820362</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.804482612265844</v>
+        <v>2.773022407577931</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.7678468760067212</v>
+        <v>0.6996044469573</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.402121811823857</v>
+        <v>5.361176354394204</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047742</v>
+        <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.309539107015333</v>
+        <v>-5.388189618735116</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.826055589309953</v>
+        <v>2.794595384622041</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.799744393091967</v>
+        <v>0.7315019640425457</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.430074292285015</v>
+        <v>5.389128834855363</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650751</v>
+        <v>3.825268416650752</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.324294431215474</v>
+        <v>-5.399339436606915</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.815791043669094</v>
+        <v>2.785773041512518</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.799744393091967</v>
+        <v>0.7315019640425457</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.425711876324212</v>
+        <v>5.38476641889456</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135745</v>
+        <v>3.845044666135747</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.274829807845562</v>
+        <v>-5.349874813237003</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.826501396433339</v>
+        <v>2.796483394276763</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.8492090164618786</v>
+        <v>0.7809665874124574</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.446315153762439</v>
+        <v>5.405369696332786</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.825931790479219</v>
+        <v>3.82593179047922</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.111721815691947</v>
+        <v>-5.186766821083387</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.888152261009719</v>
+        <v>2.858134258853143</v>
       </c>
       <c r="F2096" t="n">
-        <v>1.012317008615494</v>
+        <v>0.9440745795660727</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.540587616769542</v>
+        <v>5.49964215933989</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844243</v>
+        <v>3.847096478844245</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-4.97891419019478</v>
+        <v>-5.053959195586221</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.950322347899714</v>
+        <v>2.920304345743138</v>
       </c>
       <c r="F2097" t="n">
-        <v>1.012317008615494</v>
+        <v>0.9440745795660727</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.549634653460671</v>
+        <v>5.508689196031018</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790947</v>
+        <v>3.832425987790948</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.041622106669339</v>
+        <v>-5.116667112060779</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.926096646296013</v>
+        <v>2.896078644139436</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.9496090921409363</v>
+        <v>0.8813666630915149</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.512867368562058</v>
+        <v>5.471921911132405</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578993</v>
+        <v>3.861579399578995</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-4.993613982825646</v>
+        <v>-5.068658988217086</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.908209312623842</v>
+        <v>2.878191310467266</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.9496090921409363</v>
+        <v>0.8813666630915149</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.47577678535241</v>
+        <v>5.434831327922757</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629881</v>
+        <v>3.872253907629883</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.914788325642055</v>
+        <v>-4.989833331033496</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.943671829055228</v>
+        <v>2.913653826898652</v>
       </c>
       <c r="F2100" t="n">
-        <v>1.028434749324527</v>
+        <v>0.9601923202751054</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.527004433220515</v>
+        <v>5.486058975790862</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686404</v>
+        <v>3.868502531686405</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.722853524388182</v>
+        <v>-4.797898529779622</v>
       </c>
       <c r="E2101" t="n">
-        <v>3.015344842163815</v>
+        <v>2.985326840007239</v>
       </c>
       <c r="F2101" t="n">
-        <v>1.028434749324527</v>
+        <v>0.9601923202751054</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.521903525827552</v>
+        <v>5.480958068397899</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.84932404404671</v>
+        <v>3.849324044046712</v>
       </c>
       <c r="C2102" t="n">
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.604680146370255</v>
+        <v>-4.679725151761694</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.057968102760081</v>
+        <v>3.027950100603505</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.146608127342454</v>
+        <v>1.078365698293033</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.588161462027403</v>
+        <v>5.54721600459775</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.836463274528999</v>
+        <v>3.836463274529001</v>
       </c>
       <c r="C2103" t="n">
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.491265463587523</v>
+        <v>-4.566310468978963</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.1324225687362</v>
+        <v>3.102404566579624</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.260022810125185</v>
+        <v>1.191780381075764</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.685298864560069</v>
+        <v>5.644353407130416</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.796172938801832</v>
+        <v>3.801544742942443</v>
       </c>
       <c r="C2104" t="n">
-        <v>4.936235903995918</v>
+        <v>4.908902390633618</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.491265463587523</v>
+        <v>-4.542529986623006</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.1324225687362</v>
+        <v>3.091533971670668</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.260022810125185</v>
+        <v>1.221004432133876</v>
       </c>
       <c r="G2104" t="n">
-        <v>4.929299700982286</v>
+        <v>5.641505049913944</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20241001.xlsx
+++ b/tame_output/ON/bt/strategyON_20241001.xlsx
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.2%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.9%</t>
+          <t>421.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-615.8%</t>
+          <t>-614.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-67.1%</t>
+          <t>-66.5%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-204.2%</t>
+          <t>-204.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-101.9%</t>
+          <t>-100.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>124.2%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>112.9%</t>
+          <t>113.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>118.1%</t>
+          <t>118.9%</t>
         </is>
       </c>
     </row>
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.847178123441527</v>
+        <v>-4.828439132028496</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.630713866315488</v>
+        <v>1.6382094628807</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.5333850388395425</v>
+        <v>0.552124030252573</v>
       </c>
       <c r="G2044" t="n">
-        <v>3.889972563309572</v>
+        <v>3.90121595815739</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.888333243009748</v>
+        <v>-4.869594251596717</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.616132448672335</v>
+        <v>1.623628045237547</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.4922299192713215</v>
+        <v>0.510968910684352</v>
       </c>
       <c r="G2045" t="n">
-        <v>3.867160121752775</v>
+        <v>3.878403516600593</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.820284680318218</v>
+        <v>-4.801545688905187</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.656202899626829</v>
+        <v>1.663698496192042</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.5602784819628513</v>
+        <v>0.5790174733758818</v>
       </c>
       <c r="G2046" t="n">
-        <v>3.920840285245576</v>
+        <v>3.932083680093394</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013422</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-5.051885073487719</v>
+        <v>-5.033146082074688</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.583765412532623</v>
+        <v>1.591261009097836</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.5602784819628513</v>
+        <v>0.5790174733758818</v>
       </c>
       <c r="G2047" t="n">
-        <v>3.94104295541917</v>
+        <v>3.952286350266988</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498967</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-5.101936619016938</v>
+        <v>-5.083197627603907</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.547351030387818</v>
+        <v>1.55484662695303</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.5602784819628513</v>
+        <v>0.5790174733758818</v>
       </c>
       <c r="G2048" t="n">
-        <v>3.924649191486052</v>
+        <v>3.93589258633387</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800096</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-5.277043451593382</v>
+        <v>-5.258304460180351</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.437560210950707</v>
+        <v>1.445055807515919</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.5602784819628513</v>
+        <v>0.5790174733758818</v>
       </c>
       <c r="G2049" t="n">
-        <v>3.884901105079519</v>
+        <v>3.896144499927337</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660848</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-5.080943298162859</v>
+        <v>-5.062204306749829</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.523022891319856</v>
+        <v>1.530518487885068</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.7563786353933742</v>
+        <v>0.7751176268064047</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.009583816134772</v>
+        <v>4.02082721098259</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395085</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.927917906049575</v>
+        <v>-4.909178914636544</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.683404047738074</v>
+        <v>1.690899644303286</v>
       </c>
       <c r="F2051" t="n">
-        <v>0.9094040275066584</v>
+        <v>0.9281430189196889</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.200570050975648</v>
+        <v>4.211813445823466</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791147</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.956225219922845</v>
+        <v>-4.937486228509814</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.859547347097058</v>
+        <v>1.867042943662271</v>
       </c>
       <c r="F2052" t="n">
-        <v>0.9094040275066584</v>
+        <v>0.9281430189196889</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.388036275883939</v>
+        <v>4.399279670731758</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620433</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-5.122818445036367</v>
+        <v>-5.104079453623337</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.762313008405732</v>
+        <v>1.769808604970945</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.7428108023931359</v>
+        <v>0.7615497938061664</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.257483292169909</v>
+        <v>4.268726687017727</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-5.099782651674801</v>
+        <v>-5.081043660261771</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.775203728412076</v>
+        <v>1.782699324977289</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.7428108023931359</v>
+        <v>0.7615497938061664</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.261159694831627</v>
+        <v>4.272403089679445</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-5.070536671219105</v>
+        <v>-5.051797679806074</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.78452017571785</v>
+        <v>1.792015772283063</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.7428108023931359</v>
+        <v>0.7615497938061664</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.258777749955122</v>
+        <v>4.27002114480294</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256368</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-5.177462219096956</v>
+        <v>-5.158723227683925</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.739043195724345</v>
+        <v>1.746538792289557</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.6358852545152845</v>
+        <v>0.654624245928315</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.191915660386046</v>
+        <v>4.203159055233865</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.689942600700998</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.322480777604205</v>
+        <v>-5.303741786191174</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.68246457446468</v>
+        <v>1.689960171029892</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.490866696008036</v>
+        <v>0.5096056874210665</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.106333327424931</v>
+        <v>4.11757672227275</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.71185242968701</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.440822543388922</v>
+        <v>-5.422083551975891</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.735059107408546</v>
+        <v>1.742554703973758</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.5015527345709261</v>
+        <v>0.5202917259839566</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.212676189820418</v>
+        <v>4.223919584668237</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.7148790517908</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.49223296570963</v>
+        <v>-5.473493974296599</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.712280635606202</v>
+        <v>1.719776232171414</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.5015527345709261</v>
+        <v>0.5202917259839566</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.210461886946358</v>
+        <v>4.221705281794176</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.70475794943733</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.571652416917382</v>
+        <v>-5.552913425504351</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.68041598319739</v>
+        <v>1.687911579762602</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.5015527345709261</v>
+        <v>0.5202917259839566</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.210365015020646</v>
+        <v>4.221608409868465</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298394</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.667115414834599</v>
+        <v>-5.648376423421569</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.642224677588546</v>
+        <v>1.649720274153758</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.5015527345709261</v>
+        <v>0.5202917259839566</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.21035890857869</v>
+        <v>4.221602303426508</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715372960217996</v>
       </c>
       <c r="C2062" t="n">
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.602739503983885</v>
+        <v>-5.584000512570854</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.666071438491442</v>
+        <v>1.673567035056655</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.5659286454216412</v>
+        <v>0.5846676368346717</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.247080851651729</v>
+        <v>4.258324246499548</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736089413353532</v>
       </c>
       <c r="C2063" t="n">
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.658108666116078</v>
+        <v>-5.639369674703048</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.649657591386292</v>
+        <v>1.657153187951504</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.5659286454216412</v>
+        <v>0.5846676368346717</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.252814669399456</v>
+        <v>4.264058064247275</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113275</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.676327133113687</v>
+        <v>-5.657588141700656</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.641908567930181</v>
+        <v>1.649404164495393</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.5408222081657991</v>
+        <v>0.5595611995788295</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.237289170388883</v>
+        <v>4.248532565236701</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790272500113684</v>
       </c>
       <c r="C2065" t="n">
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.588120298966109</v>
+        <v>-5.569381307553078</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.697065694439531</v>
+        <v>1.704561291004743</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.5408222081657991</v>
+        <v>0.5595611995788295</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.257163563239201</v>
+        <v>4.26840695808702</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.794486844016436</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.482085303760799</v>
+        <v>-5.463346312347769</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.723180393046382</v>
+        <v>1.730675989611595</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.5408222081657991</v>
+        <v>0.5595611995788295</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.24086426376393</v>
+        <v>4.252107658611748</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307668</v>
       </c>
       <c r="C2067" t="n">
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.298873640627704</v>
+        <v>-5.280134649214673</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.798896007763666</v>
+        <v>1.806391604328878</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.5408222081657991</v>
+        <v>0.5595611995788295</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.243295213227976</v>
+        <v>4.254538608075793</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
         <v>3.901746294407872</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.227152193613853</v>
+        <v>-5.208413202200822</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.810528992648583</v>
+        <v>1.818024589213795</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6125436551796497</v>
+        <v>0.6312826465926802</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.269272487515662</v>
+        <v>4.280515882363481</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723789705394109</v>
       </c>
       <c r="C2069" t="n">
         <v>3.848662040329044</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.204779168006147</v>
+        <v>-5.186040176593116</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.766393948812838</v>
+        <v>1.773889545378049</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6237994062925513</v>
+        <v>0.6425383977055817</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.222941684104575</v>
+        <v>4.234185078952393</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715607446456726</v>
       </c>
       <c r="C2070" t="n">
         <v>4.0338602452144</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.237795463916892</v>
+        <v>-5.219056472503861</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.938385635333895</v>
+        <v>1.945881231899107</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5543620296257996</v>
+        <v>0.5731010210388301</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.36647746298988</v>
+        <v>4.377720857837698</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883676</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.025781471042649</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.226267828267283</v>
+        <v>-5.207528836854252</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.934917915421988</v>
+        <v>1.9424135119872</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6133626878271621</v>
+        <v>0.6321016792401926</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.393799083738946</v>
+        <v>4.405042478586765</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236294</v>
       </c>
       <c r="C2072" t="n">
         <v>4.029449583564437</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.323609329609652</v>
+        <v>-5.304870338196621</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.899649427406829</v>
+        <v>1.907145023972041</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.5689425056616737</v>
+        <v>0.5876814970747042</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.370815086961442</v>
+        <v>4.38205848180926</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427682</v>
+        <v>3.70520107942768</v>
       </c>
       <c r="C2073" t="n">
         <v>4.030700665757275</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.409465358949618</v>
+        <v>-5.390726367536588</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.86655809786368</v>
+        <v>1.874053694428893</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5265664364355387</v>
+        <v>0.5453054278485692</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.346640527618599</v>
+        <v>4.357883922466417</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
         <v>4.013119867577777</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.418302156365738</v>
+        <v>-5.399563164952707</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.845442580717734</v>
+        <v>1.852938177282947</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.519124263794188</v>
+        <v>0.5378632552072184</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.32459442585429</v>
+        <v>4.335837820702109</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667453</v>
+        <v>3.715544411667452</v>
       </c>
       <c r="C2075" t="n">
         <v>4.023284378622827</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.509684718931196</v>
+        <v>-5.490945727518166</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.8190540667366</v>
+        <v>1.826549663301813</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.4825593790748433</v>
+        <v>0.5012983704878737</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.312820006067733</v>
+        <v>4.324063400915551</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889187</v>
       </c>
       <c r="C2076" t="n">
         <v>4.125412636447095</v>
       </c>
       <c r="D2076" t="n">
-        <v>-5.49797800094419</v>
+        <v>-5.47923900953116</v>
       </c>
       <c r="E2076" t="n">
-        <v>1.925865011755671</v>
+        <v>1.933360608320883</v>
       </c>
       <c r="F2076" t="n">
-        <v>0.4942660970618498</v>
+        <v>0.5130050884748801</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.421972294684205</v>
+        <v>4.433215689532023</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409565</v>
+        <v>3.682476099409563</v>
       </c>
       <c r="C2077" t="n">
         <v>4.1284449751785</v>
       </c>
       <c r="D2077" t="n">
-        <v>-5.568890074686468</v>
+        <v>-5.550151083273438</v>
       </c>
       <c r="E2077" t="n">
-        <v>1.900532520990164</v>
+        <v>1.908028117555377</v>
       </c>
       <c r="F2077" t="n">
-        <v>0.4942660970618498</v>
+        <v>0.5130050884748801</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.42500463341561</v>
+        <v>4.436248028263428</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452569</v>
       </c>
       <c r="C2078" t="n">
         <v>4.341349808456558</v>
       </c>
       <c r="D2078" t="n">
-        <v>-5.57920617285282</v>
+        <v>-5.560467181439789</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.109310915001682</v>
+        <v>2.116806511566894</v>
       </c>
       <c r="F2078" t="n">
-        <v>0.4942660970618498</v>
+        <v>0.5130050884748801</v>
       </c>
       <c r="G2078" t="n">
-        <v>4.637909466693668</v>
+        <v>4.649152861541486</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762282</v>
       </c>
       <c r="C2079" t="n">
         <v>4.340528475368647</v>
       </c>
       <c r="D2079" t="n">
-        <v>-5.579112204835448</v>
+        <v>-5.560373213422417</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.108527169120721</v>
+        <v>2.116022765685933</v>
       </c>
       <c r="F2079" t="n">
-        <v>0.4946359584091677</v>
+        <v>0.5133749498221981</v>
       </c>
       <c r="G2079" t="n">
-        <v>4.637310050414149</v>
+        <v>4.648553445261967</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988013</v>
       </c>
       <c r="C2080" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2080" t="n">
-        <v>-5.727478432491592</v>
+        <v>-5.708739441078562</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.043412664002616</v>
+        <v>2.050908260567829</v>
       </c>
       <c r="F2080" t="n">
-        <v>0.4946359584091677</v>
+        <v>0.5133749498221981</v>
       </c>
       <c r="G2080" t="n">
-        <v>4.631542036358502</v>
+        <v>4.64278543120632</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.647907242740919</v>
       </c>
       <c r="C2081" t="n">
         <v>4.334760461313001</v>
       </c>
       <c r="D2081" t="n">
-        <v>-5.726530009373554</v>
+        <v>-5.707791017960523</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.043792033249832</v>
+        <v>2.051287629815044</v>
       </c>
       <c r="F2081" t="n">
-        <v>0.4946359584091677</v>
+        <v>0.5133749498221981</v>
       </c>
       <c r="G2081" t="n">
-        <v>4.631542036358502</v>
+        <v>4.64278543120632</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663624</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.347488069294093</v>
       </c>
       <c r="D2082" t="n">
-        <v>-5.826799827332575</v>
+        <v>-5.808060835919544</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.016411714047315</v>
+        <v>2.023907310612528</v>
       </c>
       <c r="F2082" t="n">
-        <v>0.4946359584091677</v>
+        <v>0.5133749498221981</v>
       </c>
       <c r="G2082" t="n">
-        <v>4.644269644339595</v>
+        <v>4.655513039187412</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424768</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
         <v>4.349434067718481</v>
       </c>
       <c r="D2083" t="n">
-        <v>-5.820807580543764</v>
+        <v>-5.802068589130733</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.020754611187228</v>
+        <v>2.02825020775244</v>
       </c>
       <c r="F2083" t="n">
-        <v>0.4946359584091677</v>
+        <v>0.5133749498221981</v>
       </c>
       <c r="G2083" t="n">
-        <v>4.646215642763982</v>
+        <v>4.6574590376118</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.34308820373625</v>
       </c>
       <c r="D2084" t="n">
-        <v>-5.732249619412996</v>
+        <v>-5.713510627999965</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.049831931657303</v>
+        <v>2.057327528222516</v>
       </c>
       <c r="F2084" t="n">
-        <v>0.4946359584091677</v>
+        <v>0.5133749498221981</v>
       </c>
       <c r="G2084" t="n">
-        <v>4.639869778781751</v>
+        <v>4.651113173629569</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.73530072138309</v>
+        <v>3.735300721383088</v>
       </c>
       <c r="C2085" t="n">
         <v>4.342396881175246</v>
       </c>
       <c r="D2085" t="n">
-        <v>-5.714490541909922</v>
+        <v>-5.695751550496891</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.056244240097529</v>
+        <v>2.063739836662741</v>
       </c>
       <c r="F2085" t="n">
-        <v>0.4946359584091677</v>
+        <v>0.5133749498221981</v>
       </c>
       <c r="G2085" t="n">
-        <v>4.639178456220747</v>
+        <v>4.650421851068565</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720994</v>
       </c>
       <c r="C2086" t="n">
         <v>4.355179067083832</v>
       </c>
       <c r="D2086" t="n">
-        <v>-5.614860390860854</v>
+        <v>-5.596121399447823</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.108878486425743</v>
+        <v>2.116374082990955</v>
       </c>
       <c r="F2086" t="n">
-        <v>0.5942661094582352</v>
+        <v>0.6130051008712656</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.711738732758774</v>
+        <v>4.722982127606592</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.77535709745527</v>
+        <v>3.775357097455268</v>
       </c>
       <c r="C2087" t="n">
         <v>4.544333332582559</v>
       </c>
       <c r="D2087" t="n">
-        <v>-5.664259899549865</v>
+        <v>-5.645520908136834</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.278272948448865</v>
+        <v>2.285768545014077</v>
       </c>
       <c r="F2087" t="n">
-        <v>0.6045249428899799</v>
+        <v>0.6232639343030103</v>
       </c>
       <c r="G2087" t="n">
-        <v>4.907048298316547</v>
+        <v>4.918291693164365</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963131</v>
+        <v>3.749078058963129</v>
       </c>
       <c r="C2088" t="n">
         <v>4.531522005685421</v>
       </c>
       <c r="D2088" t="n">
-        <v>-5.457575425907489</v>
+        <v>-5.438836434494458</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.348135411008677</v>
+        <v>2.355631007573889</v>
       </c>
       <c r="F2088" t="n">
-        <v>0.8112094165323556</v>
+        <v>0.8299484079453859</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.018247655604834</v>
+        <v>5.029491050452653</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162541</v>
+        <v>3.740284389162539</v>
       </c>
       <c r="C2089" t="n">
         <v>4.533523519339526</v>
       </c>
       <c r="D2089" t="n">
-        <v>-5.491732320905015</v>
+        <v>-5.472993329491985</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.336474166663772</v>
+        <v>2.343969763228984</v>
       </c>
       <c r="F2089" t="n">
-        <v>0.7276256469915431</v>
+        <v>0.7463646384045735</v>
       </c>
       <c r="G2089" t="n">
-        <v>4.970098907534452</v>
+        <v>4.98134230238227</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
         <v>4.887020633329193</v>
       </c>
       <c r="D2090" t="n">
-        <v>-5.399142841843559</v>
+        <v>-5.380403850430528</v>
       </c>
       <c r="E2090" t="n">
-        <v>2.727007072278022</v>
+        <v>2.734502668843234</v>
       </c>
       <c r="F2090" t="n">
-        <v>0.7276256469915431</v>
+        <v>0.7463646384045735</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.32359602152412</v>
+        <v>5.334839416371937</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108671</v>
+        <v>3.80905590510867</v>
       </c>
       <c r="C2091" t="n">
         <v>4.891583744896296</v>
       </c>
       <c r="D2091" t="n">
-        <v>-5.472303445616704</v>
+        <v>-5.453564454203673</v>
       </c>
       <c r="E2091" t="n">
-        <v>2.702305942335867</v>
+        <v>2.709801538901079</v>
       </c>
       <c r="F2091" t="n">
-        <v>0.6996044469573</v>
+        <v>0.7183434383703304</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.311346413070677</v>
+        <v>5.322589807918495</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103562</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
         <v>4.941413686219824</v>
       </c>
       <c r="D2092" t="n">
-        <v>-5.420087135820362</v>
+        <v>-5.401348144407331</v>
       </c>
       <c r="E2092" t="n">
-        <v>2.773022407577931</v>
+        <v>2.780518004143143</v>
       </c>
       <c r="F2092" t="n">
-        <v>0.6996044469573</v>
+        <v>0.7183434383703304</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.361176354394204</v>
+        <v>5.372419749242022</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047744</v>
+        <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
         <v>4.950227656429835</v>
       </c>
       <c r="D2093" t="n">
-        <v>-5.388189618735116</v>
+        <v>-5.369450627322085</v>
       </c>
       <c r="E2093" t="n">
-        <v>2.794595384622041</v>
+        <v>2.802090981187253</v>
       </c>
       <c r="F2093" t="n">
-        <v>0.7315019640425457</v>
+        <v>0.7502409554555762</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.389128834855363</v>
+        <v>5.400372229703181</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650752</v>
+        <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
         <v>4.945865240469032</v>
       </c>
       <c r="D2094" t="n">
-        <v>-5.399339436606915</v>
+        <v>-5.384205951522226</v>
       </c>
       <c r="E2094" t="n">
-        <v>2.785773041512518</v>
+        <v>2.791826435546394</v>
       </c>
       <c r="F2094" t="n">
-        <v>0.7315019640425457</v>
+        <v>0.7502409554555762</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.38476641889456</v>
+        <v>5.396009813742378</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.845044666135747</v>
+        <v>3.845044666135745</v>
       </c>
       <c r="C2095" t="n">
         <v>4.936789743885312</v>
       </c>
       <c r="D2095" t="n">
-        <v>-5.349874813237003</v>
+        <v>-5.334741328152314</v>
       </c>
       <c r="E2095" t="n">
-        <v>2.796483394276763</v>
+        <v>2.802536788310638</v>
       </c>
       <c r="F2095" t="n">
-        <v>0.7809665874124574</v>
+        <v>0.7997055788254879</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.405369696332786</v>
+        <v>5.416613091180604</v>
       </c>
     </row>
     <row r="2096">
@@ -49753,22 +49753,22 @@
         <v>45558</v>
       </c>
       <c r="B2096" t="n">
-        <v>3.82593179047922</v>
+        <v>3.825931790479219</v>
       </c>
       <c r="C2096" t="n">
         <v>4.933197411600246</v>
       </c>
       <c r="D2096" t="n">
-        <v>-5.186766821083387</v>
+        <v>-5.171633335998699</v>
       </c>
       <c r="E2096" t="n">
-        <v>2.858134258853143</v>
+        <v>2.864187652887018</v>
       </c>
       <c r="F2096" t="n">
-        <v>0.9440745795660727</v>
+        <v>0.9628135709791031</v>
       </c>
       <c r="G2096" t="n">
-        <v>5.49964215933989</v>
+        <v>5.510885554187708</v>
       </c>
     </row>
     <row r="2097">
@@ -49776,22 +49776,22 @@
         <v>45559</v>
       </c>
       <c r="B2097" t="n">
-        <v>3.847096478844245</v>
+        <v>3.847096478844243</v>
       </c>
       <c r="C2097" t="n">
         <v>4.942244448291374</v>
       </c>
       <c r="D2097" t="n">
-        <v>-5.053959195586221</v>
+        <v>-5.038825710501532</v>
       </c>
       <c r="E2097" t="n">
-        <v>2.920304345743138</v>
+        <v>2.926357739777013</v>
       </c>
       <c r="F2097" t="n">
-        <v>0.9440745795660727</v>
+        <v>0.9628135709791031</v>
       </c>
       <c r="G2097" t="n">
-        <v>5.508689196031018</v>
+        <v>5.519932590878836</v>
       </c>
     </row>
     <row r="2098">
@@ -49799,22 +49799,22 @@
         <v>45560</v>
       </c>
       <c r="B2098" t="n">
-        <v>3.832425987790948</v>
+        <v>3.832425987790947</v>
       </c>
       <c r="C2098" t="n">
         <v>4.943101913277496</v>
       </c>
       <c r="D2098" t="n">
-        <v>-5.116667112060779</v>
+        <v>-5.10153362697609</v>
       </c>
       <c r="E2098" t="n">
-        <v>2.896078644139436</v>
+        <v>2.902132038173312</v>
       </c>
       <c r="F2098" t="n">
-        <v>0.8813666630915149</v>
+        <v>0.9001056545045454</v>
       </c>
       <c r="G2098" t="n">
-        <v>5.471921911132405</v>
+        <v>5.483165305980223</v>
       </c>
     </row>
     <row r="2099">
@@ -49822,22 +49822,22 @@
         <v>45561</v>
       </c>
       <c r="B2099" t="n">
-        <v>3.861579399578995</v>
+        <v>3.861579399578993</v>
       </c>
       <c r="C2099" t="n">
         <v>4.906011330067848</v>
       </c>
       <c r="D2099" t="n">
-        <v>-5.068658988217086</v>
+        <v>-5.053525503132398</v>
       </c>
       <c r="E2099" t="n">
-        <v>2.878191310467266</v>
+        <v>2.884244704501141</v>
       </c>
       <c r="F2099" t="n">
-        <v>0.8813666630915149</v>
+        <v>0.9001056545045454</v>
       </c>
       <c r="G2099" t="n">
-        <v>5.434831327922757</v>
+        <v>5.446074722770575</v>
       </c>
     </row>
     <row r="2100">
@@ -49845,22 +49845,22 @@
         <v>45562</v>
       </c>
       <c r="B2100" t="n">
-        <v>3.872253907629883</v>
+        <v>3.872253907629881</v>
       </c>
       <c r="C2100" t="n">
         <v>4.909943583625799</v>
       </c>
       <c r="D2100" t="n">
-        <v>-4.989833331033496</v>
+        <v>-4.974699845948807</v>
       </c>
       <c r="E2100" t="n">
-        <v>2.913653826898652</v>
+        <v>2.919707220932528</v>
       </c>
       <c r="F2100" t="n">
-        <v>0.9601923202751054</v>
+        <v>0.9789313116881359</v>
       </c>
       <c r="G2100" t="n">
-        <v>5.486058975790862</v>
+        <v>5.49730237063868</v>
       </c>
     </row>
     <row r="2101">
@@ -49868,22 +49868,22 @@
         <v>45563</v>
       </c>
       <c r="B2101" t="n">
-        <v>3.868502531686405</v>
+        <v>3.868502531686404</v>
       </c>
       <c r="C2101" t="n">
         <v>4.904842676232835</v>
       </c>
       <c r="D2101" t="n">
-        <v>-4.797898529779622</v>
+        <v>-4.782765044694933</v>
       </c>
       <c r="E2101" t="n">
-        <v>2.985326840007239</v>
+        <v>2.991380234041114</v>
       </c>
       <c r="F2101" t="n">
-        <v>0.9601923202751054</v>
+        <v>0.9789313116881359</v>
       </c>
       <c r="G2101" t="n">
-        <v>5.480958068397899</v>
+        <v>5.492201463245717</v>
       </c>
     </row>
     <row r="2102">
@@ -49891,22 +49891,22 @@
         <v>45564</v>
       </c>
       <c r="B2102" t="n">
-        <v>3.849324044046712</v>
+        <v>3.84932404404671</v>
       </c>
       <c r="C2102" t="n">
         <v>4.900196585621931</v>
       </c>
       <c r="D2102" t="n">
-        <v>-4.679725151761694</v>
+        <v>-4.664591666677007</v>
       </c>
       <c r="E2102" t="n">
-        <v>3.027950100603505</v>
+        <v>3.03400349463738</v>
       </c>
       <c r="F2102" t="n">
-        <v>1.078365698293033</v>
+        <v>1.097104689706063</v>
       </c>
       <c r="G2102" t="n">
-        <v>5.54721600459775</v>
+        <v>5.558459399445569</v>
       </c>
     </row>
     <row r="2103">
@@ -49914,22 +49914,22 @@
         <v>45565</v>
       </c>
       <c r="B2103" t="n">
-        <v>3.836463274529001</v>
+        <v>3.836463274528999</v>
       </c>
       <c r="C2103" t="n">
         <v>4.929285178484958</v>
       </c>
       <c r="D2103" t="n">
-        <v>-4.566310468978963</v>
+        <v>-4.551176983894275</v>
       </c>
       <c r="E2103" t="n">
-        <v>3.102404566579624</v>
+        <v>3.108457960613499</v>
       </c>
       <c r="F2103" t="n">
-        <v>1.191780381075764</v>
+        <v>1.210519372488795</v>
       </c>
       <c r="G2103" t="n">
-        <v>5.644353407130416</v>
+        <v>5.655596801978235</v>
       </c>
     </row>
     <row r="2104">
@@ -49937,22 +49937,22 @@
         <v>45566</v>
       </c>
       <c r="B2104" t="n">
-        <v>3.801544742942443</v>
+        <v>3.801544742942442</v>
       </c>
       <c r="C2104" t="n">
         <v>4.908902390633618</v>
       </c>
       <c r="D2104" t="n">
-        <v>-4.542529986623006</v>
+        <v>-4.527449676492753</v>
       </c>
       <c r="E2104" t="n">
-        <v>3.091533971670668</v>
+        <v>3.097566095722769</v>
       </c>
       <c r="F2104" t="n">
-        <v>1.221004432133876</v>
+        <v>1.234246679890316</v>
       </c>
       <c r="G2104" t="n">
-        <v>5.641505049913944</v>
+        <v>5.649450398567808</v>
       </c>
     </row>
   </sheetData>
